--- a/src/assets/samples/ImportTicketCancellationTemplate.xlsx
+++ b/src/assets/samples/ImportTicketCancellationTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahmed-Nagy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DDF5FD-C94D-47A6-BADD-5A3D892AB91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF12A632-9444-471D-8385-A2D981F601A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="720" windowWidth="21975" windowHeight="20880" xr2:uid="{F8CF2A45-B278-473C-AD22-2B1052D31D43}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F8CF2A45-B278-473C-AD22-2B1052D31D43}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Terminal</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>Assignee</t>
+  </si>
+  <si>
+    <t>Terminal ID</t>
   </si>
 </sst>
 </file>
@@ -90,9 +93,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -130,7 +133,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -236,7 +239,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -378,7 +381,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -386,23 +389,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BE0C2A-D9F3-4CDC-A2FB-2EA44E3111B1}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.875" style="1"/>
+    <col min="1" max="1" width="9.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>

--- a/src/assets/samples/ImportTicketCancellationTemplate.xlsx
+++ b/src/assets/samples/ImportTicketCancellationTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahmed-Nagy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ibrahim Ali\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF12A632-9444-471D-8385-A2D981F601A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F176E651-EB70-427C-9E67-FC9F3A44D1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F8CF2A45-B278-473C-AD22-2B1052D31D43}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Terminal</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>ErrandType</t>
   </si>
@@ -47,7 +44,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -389,28 +386,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BE0C2A-D9F3-4CDC-A2FB-2EA44E3111B1}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.8984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" style="1"/>
+    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
